--- a/results/zero_shot_20.xlsx
+++ b/results/zero_shot_20.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="gpt-5" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="gpt-4o" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="gpt-5.5" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="claude-sonnet-5" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="claude-opus-4-8" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="claude-opus-4-8" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="claude-sonnet-5" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="gemini-3.5-flash" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,10 +453,14 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>bolna, rekurentna glavobolja povezana sa oslobađanjem histamina iz ćelija</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr"/>
+          <t>bolna, ponavljajuća glavobolja povezana s oslobađanjem histamina iz ćelija</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>ENG30-14326607-n</t>
@@ -463,15 +468,19 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>glavobolja; bol u glavi; cefalalgija</t>
+          <t>glavobolja; migrena; cefalalgija</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>bol u glavi koja je posledica dilatacije cerebralnih arterija, kontrakcija mišića ili reakcije na lekove</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr"/>
+          <t>bol u glavi uzrokovan širenjem moždanih arterija ili kontrakcijama mišića ili reakcijom na lekove</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -479,15 +488,9 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ENG30-14289942-n</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>površinska opekotina; ožegotina</t>
+          <t>površinska opekotina</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -495,10 +498,9 @@
           <t>površinska opekotina</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>ENG30-14289590-n</t>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -508,10 +510,14 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>povreda uzrokovana izlaganjem toploti, hemikalijama ili zračenju</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>povreda izazvana izlaganjem toploti, hemikalijama ili zračenju</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,26 +525,19 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>ENG30-09782855-n</t>
-        </is>
-      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>osoba s aleksijom</t>
+          <t>aleksičan</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>osoba s aleksijom</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>ENG30-10405694-n</t>
+          <t>osoba sa aleksijom</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -553,7 +552,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>broj pacijenata u hitnoj službi naglo je porastao</t>
+          <t>1 : broj hitnih pacijenata je brzo porastao</t>
         </is>
       </c>
     </row>
@@ -563,35 +562,24 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>ENG30-02380980-v</t>
-        </is>
-      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>odustati; povući se; istupiti; uzmaći; ustuknuti</t>
+          <t>povući se</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>odustati od preuzete obaveze</t>
+          <t>ukloniti se iz obaveze</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Odustao je kada je čuo koliko posla to podrazumeva</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>ENG30-01766952-v</t>
+          <t>1 : On se povukao kada je čuo koliko posla je uključeno</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>povući se; odustati</t>
+          <t>povući se; povući</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -601,7 +589,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Povukao se iz života kada mu je supruga umrla</t>
+          <t>1 : povukao se iz života kada mu je žena umrla</t>
         </is>
       </c>
     </row>
@@ -611,12 +599,6 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>ENG30-14159318-n</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>klinodaktilija</t>
@@ -624,26 +606,29 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>kongenitalni defekt pri kojem su jedan ili više prstiju šake ili stopala abnormalno položeni</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>ENG30-14465048-n</t>
+          <t>kongenitalna mana kod koje su jedan ili više prstiju na rukama ili nogama abnormalno pozicionirani</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>urođena mana; kongenitalna anomalija; kongenitalni defekt; kongenitalni poremećaj; kongenitalna abnormalnost</t>
+          <t>urođena mana; kongenitalna anomalija; kongenitalna mana; kongenitalni poremećaj; kongenitalna abnormalnost</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>defekt koji je prisutan pri rođenju</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>mana prisutna pri rođenju</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -651,7 +636,6 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>ENG30-05724694-n</t>
@@ -659,17 +643,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>bol; bolni osećaj</t>
+          <t>bol; bolna senzacija</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>somatski osećaj akutne nelagodnosti</t>
+          <t>somatska senzacija akutne nelagodnosti</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1 : kako se intenzitet povećavao, osećaj se promenio od golicanja do bola</t>
+          <t>1 : kako se intenzitet povećavao, senzacija se menjala od golicanja do bola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -679,12 +663,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>somestezija; somestezija; somatestezija; somatska senzacija</t>
+          <t>somestezija; somaestezija; somatestezija; somatska senzacija</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>percepcija taktilnih, proprioceptivnih ili visceralnih senzacija</t>
+          <t>percepcija taktalnih, proprioceptivnih ili visceralnih senzacija</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -699,31 +683,24 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>ENG30-00003316-v</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>udisati; udahnuti</t>
+          <t>aspirirati</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>udisati vazduh</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>ENG30-00005041-v</t>
+          <t>usisati vazduh</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>udisati; udahnuti; inhalirati</t>
+          <t>udisati; inspirisati; udahnuti</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -733,7 +710,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1 : Pacijent sa karcinomom pluća teško udiše vazduh | 2 : Duboko udahnite | 3 : Udahnite svež planinski vazduh | 4 : Pacijent ima poteškoće sa udisanjem</t>
+          <t>1 : Pacijent sa rakom pluća ne može dobro inspirisati vazduh | 2 : Duboko udahnite | 3 : udahnite svež planinski vazduh | 4 : Pacijent ima poteškoća sa inspirisanjem</t>
         </is>
       </c>
     </row>
@@ -743,7 +720,6 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>ENG30-14165240-n</t>
@@ -751,15 +727,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>hemolitička anemija</t>
+          <t>hemolitička anemija; hemolitička anemija</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>anemija nastala usled hemolize eritrocita</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
+          <t>anemija koja nastaje usled razaranja eritrocita</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>ENG30-14195315-n</t>
@@ -767,15 +747,19 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>anemija</t>
+          <t>anemija; anemija</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>smanjen broj eritrocita</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>nedostatak crvenih krvnih zrnaca</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -783,7 +767,6 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>ENG30-01426375-a</t>
@@ -796,32 +779,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>(posebno u medicini) u vezi sa bolešću ili nečim što nalikuje bolesti; koji istovremeno napada ili pogađa mnoge pojedince u zajednici ili populaciji</t>
+          <t>(posebno u medicini) bolest ili nešto što liči na bolest; napada ili pogađa mnoge pojedince u zajednici ili populaciji istovremeno</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1 : epidemijska pojava gripa</t>
+          <t>1 : epidemijski izbijanje gripa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>nan</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
     </row>
@@ -831,12 +799,6 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>ENG30-02542878-a</t>
-        </is>
-      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>autističan</t>
@@ -844,18 +806,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>koji je karakterističan za autizam ili ima autizam</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
+          <t>karakterističan za ili pati od autizma</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -863,12 +841,6 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>ENG30-06065208-n</t>
-        </is>
-      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>urologija; urogenitalna medicina</t>
@@ -879,10 +851,9 @@
           <t>grana medicine koja se bavi dijagnostikom i lečenjem poremećaja urinarnog trakta ili urogenitalnog sistema</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ENG30-06043075-n</t>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -892,10 +863,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>grane medicinske nauke koje se bave nehirurškim tehnikama</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>grane medicinske nauke koje se bave nesavremenim tehnikama</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -903,20 +878,14 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>ENG30-13551396-n</t>
-        </is>
-      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ponovno preuzimanje; ponovni unos</t>
+          <t>ponovno preuzimanje</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>proces ponovne upotrebe ili potrošnje</t>
+          <t>proces ponovnog korišćenja ili trošenja</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -924,11 +893,6 @@
           <t>1 : psihofarmakolozi su otkrili da je ponovno preuzimanje amina proces koji inaktivira monoaminske neurotransmitere</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ENG30-13571580-n</t>
-        </is>
-      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>preuzimanje</t>
@@ -936,358 +900,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>proces preuzimanja ili upotrebe ili potrošnje</t>
+          <t>proces preuzimanja, korišćenja ili trošenja</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1 : razvili su papirne salvete sa većim upijanjem tečnosti</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>medicina</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>ENG30-14326190-n</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>dismenoreja</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>bolna menstruacija</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ENG30-14322699-n</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>bol; bolnost</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>simptom nekog fizičkog oštećenja ili poremećaja</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>1 : kod pacijenta su se razvili jaki bolovi i distenzija</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>medicina</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>ENG30-02889157-a</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>nehirurški</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>koji nije hirurški</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>1 : nehirurške tehnike</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>medicina</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>ENG30-14121667-n</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>kretinizam</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>teški hipotireoidizam koji dovodi do zaostajanja u fizičkom i mentalnom razvoju</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ENG30-14121276-n</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>hipotireoidizam</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>smanjena aktivnost štitaste žlezde; žlezdani poremećaj koji nastaje usled nedovoljne produkcije hormona štitaste žlezde</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>medicina</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>ENG30-00697614-n</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>kriokauterizacija</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>primena supstance koja zamrzavanjem izaziva destrukciju tkiva</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>ENG30-00668112-n</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>kauterizacija; kauter</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>postupak koagulacije krvi i destrukcije tkiva vrućim gvožđem, kaustičnim sredstvom ili zamrzavanjem</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>medicina</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>ENG30-05666324-n</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>imunofluorescencija</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>(imunologija) tehnika koja koristi antitela konjugovana sa fluorescentnim bojilom (fluorohromom) radi proučavanja antigena u uzorku tkiva</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>ENG30-05665146-n</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>tehnika</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>praktična metoda ili veština primenjena na određeni zadatak</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>medicina</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>ENG30-14293352-n</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>stres fraktura; fraktura zamora</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>fraktura koja nastaje usled prekomerne aktivnosti, a ne kao posledica jedne specifične povrede</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>ENG30-14292090-n</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>fraktura; prelom</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>prelom čvrstih tkiva, kao što je kost</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>1 : izgleda da je do preloma došlo usled pada | 2 : bila je to nezgodna fraktura</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>medicina</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>ENG30-06049850-n</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>endokrinologija</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>grana medicine koja se bavi endokrinim žlezdama i njihovim sekretima</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>ENG30-06043075-n</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>medicina; medicinska specijalnost</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>grane medicinske nauke koje se bave nehirurškim tehnikama</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>medicina</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>ENG30-14265205-n</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>sapa; malleus</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>destruktivna i kontagiozna bakterijska bolest konja koja se može preneti na ljude</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>ENG30-14276649-n</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>zoonoza; zoonotska bolest</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>bolest životinja koja se može preneti na ljude</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
+          <t>1 : razvili su papirne salvete sa većim preuzimanjem tečnosti</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1300,7 +920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1322,14 +942,10 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>bolna rekurentna glavobolja povezana sa oslobađanjem histamina iz ćelija</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>bolna ponavljajuća glavobolja povezana sa oslobađanjem histamina iz ćelija</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr"/>
       <c r="G1" t="inlineStr">
         <is>
           <t>ENG30-14326607-n</t>
@@ -1337,7 +953,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>glavobolja; glavobolja; cefalalgija</t>
+          <t>glavobolja; cefalalgija</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -1345,11 +961,7 @@
           <t>bol u glavi izazvan dilatacijom cerebralnih arterija ili mišićnim kontrakcijama ili reakcijom na lekove</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="J1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1357,7 +969,6 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>ENG30-14289942-n</t>
@@ -1365,7 +976,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>površinska opekotina; ožegotina</t>
+          <t>površinska opekotina; opaljotina</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1373,7 +984,11 @@
           <t>površinska opekotina</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>ENG30-14289590-n</t>
@@ -1386,10 +1001,14 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>povreda izazvana izlaganjem toploti, hemikalijama ili zračenju</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>povreda nastala usled izlaganja toploti, hemikalijama ili zračenju</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1397,7 +1016,6 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>ENG30-09782855-n</t>
@@ -1405,7 +1023,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>aleksičar</t>
+          <t>aleksična osoba</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1413,7 +1031,11 @@
           <t>osoba sa aleksijom</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>ENG30-10405694-n</t>
@@ -1431,7 +1053,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>broj hitnih pacijenata je naglo porastao</t>
+          <t>broj pacijenata hitne službe naglo je porastao</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1063,6 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>ENG30-02380980-v</t>
@@ -1449,7 +1070,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>odustati; povući se; ustuknuti; odstupiti; izuzeti se</t>
+          <t>odustati; povući se; izvući se; ustuknuti; odstupiti</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1459,7 +1080,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Odustao je kada je čuo koliko je posla potrebno.</t>
+          <t>Odustao je kada je čuo koliko posla je uključeno.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1479,7 +1100,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Povukao se iz života kada mu je supruga umrla.</t>
+          <t>Povukao se iz života kada mu je žena umrla.</t>
         </is>
       </c>
     </row>
@@ -1489,7 +1110,6 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>ENG30-14159318-n</t>
@@ -1502,7 +1122,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>urođeni defekt kod kojeg su jedan ili više prstiju šake ili stopala abnormalno postavljeni</t>
+          <t>urođeni defekt kod kojeg je jedan ili više prstiju šake ili stopala abnormalno postavljeno</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1517,7 +1137,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>urođeni defekt; kongenitalna anomalija; kongenitalni defekt; kongenitalni poremećaj; kongenitalna abnormalnost</t>
+          <t>urođena mana; kongenitalna anomalija; kongenitalni defekt; kongenitalni poremećaj; kongenitalna abnormalnost</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1537,7 +1157,6 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>ENG30-05724694-n</t>
@@ -1555,7 +1174,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>kako se intenzitet povećavao, senzacija se promenila iz golicanja u bol</t>
+          <t>1 : kako se intenzitet povećavao, senzacija se promenila iz golicanja u bol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1565,7 +1184,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>somestezija; somatska senzacija</t>
+          <t>somestezija; somaestezija; somatestezija; somatska senzacija</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1575,7 +1194,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>oslanjao se na somesteziju da ga upozori na promene pritiska</t>
+          <t>1 : oslanjao se na somesteziju da ga upozori na promene pritiska</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1204,6 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>ENG30-00003316-v</t>
@@ -1598,12 +1216,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>usisati vazduh</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>uvlačiti vazduh</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1613,17 +1226,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>inhalirati; inspirisati; udahnuti</t>
+          <t>udisati; inspirisati; udahnuti</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>uvući (vazduh)</t>
+          <t>uvlačiti vazduh</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1 : Pacijent sa karcinomom pluća ne može dobro da inspirira vazduh | 2 : Duboko udahnite | 3 : udahnuti svež planinski vazduh | 4 : Pacijent ima teškoće pri inspiraciji</t>
+          <t>1 : Pacijent sa karcinomom pluća ne može dobro da udiše vazduh | 2 : Duboko udahnite | 3 : Udahnite svež planinski vazduh | 4 : Pacijent ima teškoće pri udisanju</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1246,6 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>ENG30-14165240-n</t>
@@ -1649,7 +1261,11 @@
           <t>anemija koja nastaje usled destrukcije eritrocita</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>ENG30-14195315-n</t>
@@ -1665,7 +1281,11 @@
           <t>nedostatak crvenih krvnih zrnaca</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1673,7 +1293,6 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>ENG30-01426375-a</t>
@@ -1686,12 +1305,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>(posebno u medicini) koji se odnosi na bolest ili nešto što nalikuje bolesti; koji istovremeno napada ili zahvata mnoge pojedince u zajednici ili populaciji</t>
+          <t>(naročito u medicini) koji se odnosi na bolest ili bilo šta što nalikuje bolesti; koji istovremeno napada ili pogađa veliki broj pojedinaca u zajednici ili populaciji</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>epidemijsko izbijanje gripa</t>
+          <t>epidemijska pojava gripa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1721,7 +1340,6 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>ENG30-02542878-a</t>
@@ -1734,7 +1352,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>karakterističan za autizam ili koji boluje od autizma</t>
+          <t>karakterističan za autizam ili koji ima autizam</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1769,7 +1387,6 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>ENG30-06065208-n</t>
@@ -1817,7 +1434,6 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>ENG30-13551396-n</t>
@@ -1830,7 +1446,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>proces ponovnog iskorišćavanja ili potrošnje</t>
+          <t>proces ponovnog korišćenja ili potrošnje</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1845,401 +1461,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>preuzimanje; unos; apsorpcija</t>
+          <t>preuzimanje; unos</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>proces preuzimanja, iskorišćavanja ili potrošnje</t>
+          <t>proces preuzimanja, korišćenja ili potrošnje</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>razvili su papirne salvete sa većom sposobnošću apsorpcije tečnosti</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>medicina</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>ENG30-14326190-n</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>dismenoreja</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>bolna menstruacija</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ENG30-14322699-n</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>bol; bolnost</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>simptom neke fizičke povrede ili poremećaja</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>pacijent je razvio jak bol i distenziju</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>medicina</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>ENG30-02889157-a</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>nehirurški</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>koji nije hirurški</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>nehirurške tehnike</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>medicina</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>ENG30-14121667-n</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>kretenizam</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>težak hipotireoidizam koji dovodi do zastoja u fizičkom i mentalnom razvoju</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ENG30-14121276-n</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>hipotireoidizam</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>hipofunkcija štitaste žlezde; endokrini poremećaj koji nastaje usled nedovoljne proizvodnje hormona štitaste žlezde</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>medicina</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>ENG30-00697614-n</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>kriokauterizacija</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>primena supstance koja uništava tkivo zamrzavanjem</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>ENG30-00668112-n</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>kauterija; kauterizacija</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>postupak koagulacije krvi i uništavanja tkiva vrelim gvožđem, kaustičnim sredstvom ili zamrzavanjem</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>medicina</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>ENG30-05666324-n</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>imunofluorescencija</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>(imunologija) tehnika koja koristi antitela vezana za fluorescentnu boju radi proučavanja antigena u uzorku tkiva</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>ENG30-05665146-n</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>tehnika</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>praktična metoda ili veština primenjena na određeni zadatak</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>medicina</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>ENG30-14293352-n</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>prelom zamora; stres fraktura</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>prelom koji nastaje usled prekomerne aktivnosti, a ne usled specifične povrede</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>ENG30-14292090-n</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>fraktura; prelom</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>prelom tvrdog tkiva kao što je kost</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>1 : čini se da je prelom izazvan padom | 2 : bila je to teška fraktura</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>medicina</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>ENG30-06049850-n</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>endokrinologija</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>grana medicine koja se bavi endokrinim žlezdama i njihovim sekretima</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>ENG30-06043075-n</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>medicina; medicinska specijalnost</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>grane medicinske nauke koje se bave nehirurškim tehnikama</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>medicina</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>ENG30-14265205-n</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>sakagija; maleus</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>destruktivna i zarazna bakterijska bolest konja koja se može preneti na ljude</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>ENG30-14276649-n</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>zoonoza; zoonotska bolest</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>bolest životinja koja se može preneti na ljude</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>razvili su papirne salvete sa većom sposobnošću upijanja tečnosti</t>
         </is>
       </c>
     </row>
@@ -2254,7 +1486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2276,14 +1508,10 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>bolna glavobolja koja se ponavlja, povezana sa oslobađanjem histamina iz ćelija</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>bolna ponavljajuća glavobolja povezana sa oslobađanjem histamina iz ćelija</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr"/>
       <c r="G1" t="inlineStr">
         <is>
           <t>ENG30-14326607-n</t>
@@ -2296,14 +1524,10 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>bol u glavi izazvan dilatacijom cerebralnih arterija ili mišićnim kontrakcijama ili reakcijom na lekove</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>bol u glavi uzrokovan širenjem moždanih arterija ili kontrakcijama mišića ili reakcijom na lekove</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2311,7 +1535,6 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>ENG30-14289942-n</t>
@@ -2319,17 +1542,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>opekotina; površinska opekotina</t>
+          <t>površinska opekotina</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>površinska opekotina</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>opekotina na površini kože</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -2344,12 +1562,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>povreda nastala usled izlaganja toploti, hemikalijama ili zračenju</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>povreda izazvana izlaganjem toploti, hemikalijama ili zračenju</t>
         </is>
       </c>
     </row>
@@ -2359,7 +1572,6 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>ENG30-09782855-n</t>
@@ -2375,11 +1587,6 @@
           <t>osoba koja boluje od aleksije</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>ENG30-10405694-n</t>
@@ -2397,7 +1604,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>broj hitnih pacijenata se brzo povećao</t>
+          <t>1 : broj hitnih pacijenata je naglo porastao</t>
         </is>
       </c>
     </row>
@@ -2407,7 +1614,6 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>ENG30-02380980-v</t>
@@ -2415,17 +1621,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>povući se; odustati; predomisliti se; povući se iz straha; odustati u poslednjem trenutku</t>
+          <t>povući se; odustati; odustati od obaveze</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>povući se iz obaveze</t>
+          <t>osloboditi sebe neke obaveze</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1 : Povukao se kada je čuo koliko je posla u pitanju</t>
+          <t>1 : Odustao je kada je čuo koliko je posla bilo uključeno</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -2435,7 +1641,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>povući se; odstupiti</t>
+          <t>povući se; odustati</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -2445,7 +1651,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1 : povukao se iz života kada mu je žena umrla</t>
+          <t>1 : povukao se iz života kada mu je supruga umrla</t>
         </is>
       </c>
     </row>
@@ -2455,7 +1661,6 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>ENG30-14159318-n</t>
@@ -2468,12 +1673,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>urođena mana kod koje su jedan ili više prstiju na rukama ili nogama abnormalno postavljeni</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>urođeni defekt kod kojeg su jedan ili više prstiju na nogama ili rukama nepravilno postavljeni</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2483,17 +1683,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>urođena mana; kongenitalna anomalija; urođeni defekt; kongenitalni poremećaj; urođena abnormalnost</t>
+          <t>urođeni defekt; kongenitalna anomalija; kongenitalni defekt; kongenitalni poremećaj; urođena abnormalnost</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>mana koja je prisutna od rođenja</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>defekt koji je prisutan pri rođenju</t>
         </is>
       </c>
     </row>
@@ -2503,7 +1698,6 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>ENG30-05724694-n</t>
@@ -2511,7 +1705,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>bol; bolan osećaj</t>
+          <t>bol; bolni osećaj</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2521,7 +1715,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1 : kako se intenzitet povećavao, osećaj se menjao od golicanja do bola</t>
+          <t>1 : kako je intenzitet rastao, osećaj se menjao od golicanja do bola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2531,17 +1725,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>somestezija; somatska čulnost; somatski osećaj</t>
+          <t>somestezija; somatska senzacija</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>percepcija taktilnih ili proprioceptivnih ili visceralnih osećaja</t>
+          <t>percepcija taktilnih, proprioceptivnih ili visceralnih osećaja</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1 : oslanjao se na somesteziju da ga upozori na promene pritiska</t>
+          <t>1 : oslanjao se na somesteziju da bi ga upozorila na promene pritiska</t>
         </is>
       </c>
     </row>
@@ -2551,7 +1745,6 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>ENG30-00003316-v</t>
@@ -2559,17 +1752,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>aspirovati</t>
+          <t>aspirirati; udahnuti</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>usisati vazduh</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>udisati vazduh</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2579,17 +1767,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>udisati; inhalirati; udahnuti</t>
+          <t>udisati; udahnuti</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>uvući (vazduh)</t>
+          <t>uvlačiti (vazduh)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1 : Pacijent obolio od raka pluća ne može dobro da udiše vazduh | 2 : Duboko udahnite | 3 : udisati svež planinski vazduh | 4 : Pacijent ima poteškoća sa udisanjem</t>
+          <t>1 : Pacijent sa rakom pluća ne može dobro da udahne vazduh | 2 : Udahnite duboko | 3 : udahnite svež planinski vazduh | 4 : Pacijent ima poteškoće pri udisanju</t>
         </is>
       </c>
     </row>
@@ -2599,7 +1787,6 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>ENG30-14165240-n</t>
@@ -2607,7 +1794,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>hemolitička anemija; hemolizna anemija</t>
+          <t>hemolitička anemija</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2615,11 +1802,6 @@
           <t>anemija koja nastaje usled razaranja eritrocita</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>ENG30-14195315-n</t>
@@ -2627,17 +1809,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>anemija</t>
+          <t>anemija; malokrvnost</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>nedostatak crvenih krvnih zrnaca</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
     </row>
@@ -2647,7 +1824,6 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>ENG30-01426375-a</t>
@@ -2655,37 +1831,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>epidemijski, epidemičan</t>
+          <t>epidemijski</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>(naročito u medicini) koji se odnosi na bolest ili nešto što liči na bolest; koji napada ili pogađa mnoge pojedince u zajednici ili populaciji istovremeno</t>
+          <t>(naročito u medicini) koji se odnosi na bolest ili nešto što podseća na bolest; koji istovremeno napada ili pogađa mnoge pojedince u zajednici ili populaciji</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>1 : epidemijska pojava gripa</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
     </row>
@@ -2695,7 +1851,6 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>ENG30-02542878-a</t>
@@ -2703,37 +1858,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>autističan, autistički</t>
+          <t>autistični</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>koji je karakterističan za autizam ili boluje od autizma</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>karakterističan za autizam ili koji boluje od autizma</t>
         </is>
       </c>
     </row>
@@ -2743,7 +1873,6 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>ENG30-06065208-n</t>
@@ -2756,12 +1885,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>grana medicine koja se bavi dijagnostikom i lečenjem poremećaja urinarnog trakta ili urogenitalnog sistema</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>grana medicine koja se bavi dijagnostikovanjem i lečenjem poremećaja mokraćnih puteva ili urogenitalnog sistema</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2777,11 +1901,6 @@
       <c r="I11" t="inlineStr">
         <is>
           <t>grane medicinske nauke koje se bave nehirurškim tehnikama</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>-</t>
         </is>
       </c>
     </row>
@@ -2791,7 +1910,6 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>ENG30-13551396-n</t>
@@ -2799,12 +1917,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ponovno preuzimanje; reuptake</t>
+          <t>preuzimanje; ponovno preuzimanje</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>proces ponovnog trošenja ili ponovnog korišćenja</t>
+          <t>proces ponovnog trošenja ili iskorišćavanja</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2819,401 +1937,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>preuzimanje</t>
+          <t>usvajanje</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>proces uzimanja, trošenja ili korišćenja</t>
+          <t>proces preuzimanja, iskorišćavanja ili trošenja</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1 : razvili su papirne salvete sa većim stepenom upijanja tečnosti</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>medicina</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>ENG30-14326190-n</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>dismenoreja</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>bolna menstruacija</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ENG30-14322699-n</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>bol</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>simptom neke fizičke povrede ili poremećaja</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>kod pacijenta su se razvili jak bol i nadutost</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>medicina</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>ENG30-02889157-a</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>nehirurški</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>koji nije hirurški</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>1 : nehirurške tehnike</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>medicina</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>ENG30-14121667-n</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>kretinizam</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>teški hipotireoidizam koji dovodi do fizičkog i mentalnog zastoja u razvoju</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ENG30-14121276-n</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>hipotireoidizam</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>smanjena funkcija štitne žlezde; poremećaj žlezde koji nastaje zbog nedovoljne proizvodnje hormona štitne žlezde</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>medicina</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>ENG30-00697614-n</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>kriokauterizacija</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>primena supstance koja uništava tkivo zamrzavanjem</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>ENG30-00668112-n</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>kauterizacija</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>čin koagulacije krvi i uništavanja tkiva vrelim gvožđem ili kaustičnim sredstvom ili zamrzavanjem</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>medicina</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>ENG30-05666324-n</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>imunofluorescencija</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>(imunologija) tehnika koja koristi antitela vezana za fluorescentnu boju radi proučavanja antigena u uzorku tkiva</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>ENG30-05665146-n</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>tehnika</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>praktičan metod ili veština primenjena na neki određeni zadatak</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>medicina</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>ENG30-14293352-n</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>zamorni prelom; stres prelom</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>prelom koji nastaje usled prekomerne aktivnosti, a ne usled specifične povrede</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>ENG30-14292090-n</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>prelom; fraktura</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>lom tvrdog tkiva kao što je kost</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>1 : čini se da je prelom nastao usled pada | 2 : bio je to ružan prelom</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>medicina</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>ENG30-06049850-n</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>endokrinologija</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>grana medicine koja se bavi endokrinim žlezdama i njihovim sekretima</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>ENG30-06043075-n</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>medicina; medicinska specijalnost</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>grane medicinske nauke koje se bave nehirurškim tehnikama</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>medicina</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>ENG30-14265205-n</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>sakagija</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>razorna i zarazna bakterijska bolest konja koja se može preneti na ljude</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>ENG30-14276649-n</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>zoonoza; zoonotska bolest</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>životinjska bolest koja se može preneti na ljude</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>1 : razvili su papirne salvete sa većim usvajanjem tečnosti</t>
         </is>
       </c>
     </row>
@@ -3228,7 +1962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3250,10 +1984,14 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>bolna, ponavljajuća glavobolja povezana sa oslobađanjem histamina iz ćelija</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr"/>
+          <t>bolna glavobolja koja se ponavlja, povezana sa oslobađanjem histamina iz ćelija</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>ENG30-14326607-n</t>
@@ -3266,10 +2004,14 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>bol u glavi uzrokovan proširenjem moždanih arterija ili kontrakcijama mišića ili reakcijom na lekove</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr"/>
+          <t>bol u glavi izazvan širenjem cerebralnih arterija ili kontrakcijama mišića ili reakcijom na lekove</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3277,7 +2019,6 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>ENG30-14289942-n</t>
@@ -3285,7 +2026,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>površinska opekotina; oparotina</t>
+          <t>opekotina; površinska opekotina</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3293,7 +2034,11 @@
           <t>površinska opekotina</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>ENG30-14289590-n</t>
@@ -3306,10 +2051,14 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>povreda izazvana izlaganjem toploti, hemikalijama ili zračenju</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>povreda nastala usled izloženosti toploti, hemikalijama ili zračenju</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3317,7 +2066,11 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>ENG30-09782855-n</t>
@@ -3330,10 +2083,14 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>osoba sa aleksijom</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>osoba koja boluje od aleksije</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>ENG30-10405694-n</t>
@@ -3351,7 +2108,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1 : broj hitnih pacijenata je naglo porastao</t>
+          <t>broj hitnih pacijenata je brzo porastao</t>
         </is>
       </c>
     </row>
@@ -3361,7 +2118,6 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>ENG30-02380980-v</t>
@@ -3369,17 +2125,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>povući se; odustati; odstupiti; ustuknuti</t>
+          <t>predomisliti se; povući se; odustati; uzmaći; povući se iz obaveze</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>osloboditi sebe od obaveze</t>
+          <t>osloboditi se obaveze; povući se od preuzete obaveze</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1 : Odustao je kada je čuo koliko posla to podrazumeva</t>
+          <t>1 : Predomislio se kada je čuo koliko je posla uključeno</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3389,7 +2145,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>povući se; odustati</t>
+          <t>povući se; odstupiti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -3409,7 +2165,6 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>ENG30-14159318-n</t>
@@ -3422,10 +2177,14 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>urođeni defekt kod kojeg su jedan ili više prstiju na nogama ili rukama nenormalno postavljeni</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>urođena mana kod koje su jedan ili više prstiju na rukama ili nogama abnormalno postavljeni</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>ENG30-14465048-n</t>
@@ -3433,15 +2192,19 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>urođeni defekt; urođena anomalija; kongenitalni defekt; kongenitalni poremećaj; kongenitalna anomalija</t>
+          <t>urođena mana; kongenitalna anomalija; urođeni defekt; kongenitalni poremećaj; urođena abnormalnost</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>defekt koji je prisutan na rođenju</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>mana koja je prisutna od rođenja</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3449,7 +2212,6 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>ENG30-05724694-n</t>
@@ -3457,7 +2219,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>bol; bolni osećaj</t>
+          <t>bol; bolan osećaj</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -3477,7 +2239,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>somestezija; somatski osećaj</t>
+          <t>somestezija; somatska senzacija</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -3497,7 +2259,6 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>ENG30-00003316-v</t>
@@ -3505,15 +2266,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>aspirirati; udahnuti</t>
+          <t>aspirirati</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>uvući vazduh</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+          <t>usisati vazduh</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>ENG30-00005041-v</t>
@@ -3521,17 +2286,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>udahnuti; udisati; uvlačiti vazduh</t>
+          <t>udahnuti; inspirisati; udisati</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>uvlačiti (vazduh)</t>
+          <t>uvući (vazduh)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1 : Pacijent sa karcinomom pluća ne može dobro da udahne vazduh | 2 : Udahnite duboko | 3 : udišite svež planinski vazduh | 4 : Pacijent ima poteškoće pri udisanju</t>
+          <t>1 : Pacijent obolео od raka pluća ne može dobro da udiše vazduh | 2 : Duboko udahnite | 3 : udahnite svež planinski vazduh | 4 : Pacijent ima poteškoća sa udisanjem</t>
         </is>
       </c>
     </row>
@@ -3541,7 +2306,6 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>ENG30-14165240-n</t>
@@ -3557,7 +2321,11 @@
           <t>anemija koja nastaje usled razaranja eritrocita</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>ENG30-14195315-n</t>
@@ -3565,15 +2333,19 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>anemija; malokrvnost</t>
+          <t>anemija</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>nedostatak crvenih krvnih zrnaca</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>smanjen broj eritrocita</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3581,7 +2353,6 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>ENG30-01426375-a</t>
@@ -3589,23 +2360,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>epidemijski</t>
+          <t>epidemijski, epidemički</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>(naročito u medicini) koji se odnosi na bolest ili nešto što liči na bolest; koji istovremeno napada ili pogađa mnoge pojedince u zajednici ili populaciji</t>
+          <t>(naročito u medicini) koji se odnosi na bolest ili nešto što podseća na bolest; koji napada ili zahvata mnoge pojedince u zajednici ili populaciji istovremeno</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1 : epidemijska pojava gripa</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>epidemijska pojava gripa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3613,7 +2400,6 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>ENG30-02542878-a</t>
@@ -3621,19 +2407,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>autistični, autističan</t>
+          <t>autističan</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>karakterističan za autizam ili koji boluje od autizma</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>koji je karakterističan za autizam ili boluje od autizma</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3641,7 +2447,6 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>ENG30-06065208-n</t>
@@ -3654,10 +2459,14 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>grana medicine koja se bavi dijagnostikom i lečenjem oboljenja mokraćnog trakta ili urogenitalnog sistema</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
+          <t>grana medicine koja se bavi dijagnostikom i lečenjem poremećaja urinarnog trakta ili urogenitalnog sistema</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>ENG30-06043075-n</t>
@@ -3673,7 +2482,11 @@
           <t>grane medicinske nauke koje se bave nehirurškim tehnikama</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3681,7 +2494,6 @@
           <t>medicina</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>ENG30-13551396-n</t>
@@ -3689,12 +2501,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ponovno preuzimanje; reuptejk</t>
+          <t>ponovno preuzimanje; reapsorpcija</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>proces ponovnog trošenja ili iskorišćavanja</t>
+          <t>proces ponovnog trošenja ili konzumiranja</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3714,7 +2526,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>proces preuzimanja ili trošenja ili iskorišćavanja</t>
+          <t>proces preuzimanja, trošenja ili konzumiranja</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -3723,337 +2535,531 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>medicina</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>ENG30-14326190-n</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>dismenoreja</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>bolna menstruacija</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ENG30-14322699-n</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>bol</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>simptom neke fizičke povrede ili poremećaja</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>1 : kod pacijenta se razvio jak bol i nadutost</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>medicina</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>ENG30-02889157-a</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>nehirurški</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>koji nije hirurški</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>1 : nehirurške tehnike</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>medicina</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>ENG30-14121667-n</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>kretenizam</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>teški hipotireoidizam koji dovodi do zaostajanja u fizičkom i mentalnom razvoju</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ENG30-14121276-n</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>hipotireoidizam</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>smanjena aktivnost štitaste žlezde; poremećaj žlezde koji nastaje usled nedovoljne proizvodnje hormona štitaste žlezde</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>medicina</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>ENG30-00697614-n</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>kriokauterizacija</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>primena supstance koja uništava tkivo njegovim zamrzavanjem</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>ENG30-00668112-n</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>kauterizacija</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>postupak koagulacije krvi i uništavanja tkiva užarenim gvožđem ili kaustičnim sredstvom ili zamrzavanjem</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>medicina</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>ENG30-05666324-n</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>imunofluorescencija</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>(imunologija) tehnika koja koristi antitela vezana za fluorescentnu boju radi proučavanja antigena u uzorku tkiva</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>ENG30-05665146-n</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>tehnika</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>praktičan metod ili veština primenjena na neki određeni zadatak</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>medicina</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>ENG30-14293352-n</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>stres fraktura; zamorni prelom</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>prelom koji nastaje usled prekomerne aktivnosti, a ne usled specifične povrede</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>ENG30-14292090-n</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>fraktura; prelom</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>prelom tvrdog tkiva kao što je kost</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>1 : čini se da je prelom nastao usled pada | 2 : bila je to gadna fraktura</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>medicina</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>ENG30-06049850-n</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>endokrinologija</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>grana medicine koja se bavi endokrinim žlezdama i njihovim sekretima</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>medicina</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ENG30-14327543-n</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>histaminska glavobolja; klaster glavobolja</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>bolna rekurentna glavobolja povezana sa oslobađanjem histamina iz ćelija</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ENG30-14326607-n</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>glavobolja; cefalalgija</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>bol u glavi uzrokovan dilatacijom cerebralnih arterija, kontrakcijom mišića ili reakcijom na lekove</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>medicina</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ENG30-14289942-n</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>površinska opekotina; opaljotina</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>opekotina na samoj površini kože</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ENG30-14289590-n</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>opekotina</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>povreda uzrokovana izlaganjem toploti, hemikalijama ili zračenju</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>medicina</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ENG30-09782855-n</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>aleksičar, osoba sa aleksijom</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>osoba koja pati od aleksije</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ENG30-10405694-n</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>pacijent</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>osoba kojoj je potrebna medicinska nega</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>1 : broj hitnih pacijenata je naglo porastao</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>medicina</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ENG30-02380980-v</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>povući se; odustati; ustuknuti</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>povući se iz neke obaveze</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1 : Povukao se kada je čuo koliko posla to zahteva</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ENG30-01766952-v</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>povući se</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>izgubiti interesovanje</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1 : povukao se iz života kada mu je supruga umrla</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>medicina</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ENG30-14159318-n</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>klinodaktilija</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>urođeni defekt u kojem su jedan ili više prstiju na rukama ili nogama u abnormalnom položaju</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ENG30-14465048-n</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>urođeni defekt; urođena anomalija; urođeni poremećaj; kongenitalna anomalija; kongenitalni poremećaj</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>defekt koji je prisutan na rođenju</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>medicina</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ENG30-05724694-n</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>bol; bolni osećaj</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>somatski osećaj akutne nelagodnosti</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1 : kako se intenzitet povećavao, osećaj se promenio od golicanja u bol</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ENG30-05721180-n</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>somestezija; somatski senzibilitet; somatski osećaj</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>percepcija taktilnih, proprioceptivnih ili visceralnih senzacija</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>1 : oslanjao se na somesteziju da bi ga upozorila na promene pritiska</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>medicina</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ENG30-00003316-v</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>aspirirati</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>usisavati vazduh</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ENG30-00005041-v</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>udahnuti; udisati</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>uvlačiti vazduh u pluća</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1 : Pacijent sa karcinomom pluća ne može dobro da udahne vazduh | 2 : Udahnite duboko | 3 : udisati svež planinski vazduh | 4 : Pacijent ima poteškoća sa udisanjem</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>medicina</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ENG30-14165240-n</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>hemolitička anemija</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>anemija koja nastaje usled razaranja eritrocita</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ENG30-14195315-n</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>anemija; malokrvnost</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>nedostatak crvenih krvnih zrnaca</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>medicina</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ENG30-01426375-a</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>epidemijski</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>(posebno u medicini) koji se odnosi na bolest ili nešto što nalikuje bolesti; koji istovremeno napada ili pogađa veliki broj pojedinaca u zajednici ili populaciji</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>epidemijska pojava gripa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>medicina</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ENG30-02542878-a</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>autističan</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>koji je karakterističan za autizam ili osobu koja boluje od autizma</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>medicina</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ENG30-06065208-n</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>urologija; urogenitalna medicina</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>grana medicine koja se bavi dijagnostikom i lečenjem poremećaja urinarnog trakta ili urogenitalnog sistema</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>ENG30-06043075-n</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>medicina; medicinska specijalnost</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>grane medicinske nauke koje se bave nehirurškim tehnikama</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>medicina</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>ENG30-14265205-n</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>sakagija; malej</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>razorna i zarazna bakterijska bolest konja koja se može preneti na ljude</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>ENG30-14276649-n</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>zoonoza; zoonotska bolest</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>životinjska bolest koja se može preneti na ljude</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
